--- a/app/financebase/statics/import/jdwallet.xlsx
+++ b/app/financebase/statics/import/jdwallet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26860" windowHeight="14500"/>
+    <workbookView windowWidth="26860" windowHeight="14500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="结算表" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="57">
   <si>
     <t>订单编号</t>
   </si>
@@ -96,6 +96,84 @@
     <t>商品数量</t>
   </si>
   <si>
+    <t>50700125070112003756139201</t>
+  </si>
+  <si>
+    <t>订单</t>
+  </si>
+  <si>
+    <t>商品保险服务费</t>
+  </si>
+  <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>应付</t>
+  </si>
+  <si>
+    <t>2025年11月1日代收付服务费</t>
+  </si>
+  <si>
+    <t>JD1931484741662599318195111766</t>
+  </si>
+  <si>
+    <t>支出</t>
+  </si>
+  <si>
+    <t>10100125070112003885729801</t>
+  </si>
+  <si>
+    <t>美缝胶专用工具勾缝剂</t>
+  </si>
+  <si>
+    <t>广告联合活动降扣佣金</t>
+  </si>
+  <si>
+    <t>2025年11月1日费项</t>
+  </si>
+  <si>
+    <t>10100125062911976022846601</t>
+  </si>
+  <si>
+    <t>售后服务单</t>
+  </si>
+  <si>
+    <t>货款</t>
+  </si>
+  <si>
+    <t>2025年11月1日京东支付货款</t>
+  </si>
+  <si>
+    <t>10100125070112012420693301</t>
+  </si>
+  <si>
+    <t>应收</t>
+  </si>
+  <si>
+    <t>收入</t>
+  </si>
+  <si>
+    <t>53300125070112017614079001</t>
+  </si>
+  <si>
+    <t>2025年11月1日微信等其他支付方式货款</t>
+  </si>
+  <si>
+    <t>50700125070112005076136401</t>
+  </si>
+  <si>
+    <t>JD1931484741662599323616093412</t>
+  </si>
+  <si>
+    <t>10100125070112007917359701</t>
+  </si>
+  <si>
+    <t>佣金</t>
+  </si>
+  <si>
+    <t>53300125070112006006050001</t>
+  </si>
+  <si>
     <t>商户号</t>
   </si>
   <si>
@@ -118,6 +196,9 @@
   </si>
   <si>
     <t>交易备注</t>
+  </si>
+  <si>
+    <t>--</t>
   </si>
 </sst>
 </file>
@@ -738,6 +819,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1064,15 +1148,22 @@
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="29.6428571428571" customWidth="1"/>
-    <col min="3" max="3" width="11.3035714285714" customWidth="1"/>
+    <col min="3" max="3" width="11.7142857142857" customWidth="1"/>
     <col min="4" max="4" width="16.2142857142857" customWidth="1"/>
     <col min="5" max="5" width="36.3571428571429" customWidth="1"/>
-    <col min="6" max="6" width="38.5357142857143" customWidth="1"/>
+    <col min="6" max="6" width="22.7678571428571" customWidth="1"/>
     <col min="7" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="16.8571428571429" customWidth="1"/>
     <col min="10" max="10" width="22.9285714285714" customWidth="1"/>
+    <col min="11" max="11" width="7.57142857142857" customWidth="1"/>
+    <col min="12" max="12" width="5.57142857142857" customWidth="1"/>
+    <col min="13" max="13" width="15.4285714285714" customWidth="1"/>
     <col min="14" max="14" width="38.5714285714286" customWidth="1"/>
+    <col min="15" max="15" width="7.57142857142857" customWidth="1"/>
+    <col min="16" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="9.57142857142857" customWidth="1"/>
     <col min="19" max="19" width="34.1428571428571" customWidth="1"/>
+    <col min="20" max="22" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1143,77 +1234,509 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="7:9">
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="7:9">
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="7:9">
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="7:9">
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="7:9">
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="7:9">
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="7:9">
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="7:9">
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="7:9">
+    <row r="2" customFormat="1" spans="1:22">
+      <c r="A2" t="str">
+        <f>"318195111766"</f>
+        <v>318195111766</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="str">
+        <f>"0"</f>
+        <v>0</v>
+      </c>
+      <c r="E2" t="str">
+        <f>"20251102014741140018161002610171"</f>
+        <v>20251102014741140018161002610171</v>
+      </c>
+      <c r="G2" s="1">
+        <v>45962.0224652778</v>
+      </c>
+      <c r="H2" s="1">
+        <v>45962.0228587963</v>
+      </c>
+      <c r="I2" s="1">
+        <v>45963.5418634259</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2">
+        <v>-0.28</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2">
+        <v>782412</v>
+      </c>
+      <c r="S2" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2">
+        <v>20251101</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:22">
+      <c r="A3" t="str">
+        <f>"322835262118"</f>
+        <v>322835262118</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="str">
+        <f>"10113589944177"</f>
+        <v>10113589944177</v>
+      </c>
+      <c r="E3" t="str">
+        <f>"20251102014741140018161002610190"</f>
+        <v>20251102014741140018161002610190</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="1">
+        <v>45955.6654861111</v>
+      </c>
+      <c r="H3" s="1">
+        <v>45955.667662037</v>
+      </c>
+      <c r="I3" s="1">
+        <v>45963.5418634259</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3">
+        <v>-0.67</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3">
+        <v>782412</v>
+      </c>
+      <c r="T3" t="s">
+        <v>29</v>
+      </c>
+      <c r="U3">
+        <v>20251101</v>
+      </c>
+      <c r="V3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:22">
+      <c r="A4" t="str">
+        <f>"322457330375"</f>
+        <v>322457330375</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="str">
+        <f>"10053464760522"</f>
+        <v>10053464760522</v>
+      </c>
+      <c r="E4" t="str">
+        <f>"20251102014741140018161002610149"</f>
+        <v>20251102014741140018161002610149</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="1">
+        <v>45959.9460416667</v>
+      </c>
+      <c r="H4" s="1">
+        <v>45959.9509143519</v>
+      </c>
+      <c r="I4" s="1">
+        <v>45963.5418634259</v>
+      </c>
+      <c r="J4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4">
+        <v>-23.67</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4">
+        <v>782412</v>
+      </c>
+      <c r="T4" t="s">
+        <v>29</v>
+      </c>
+      <c r="U4">
+        <v>20251101</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:22">
+      <c r="A5" t="str">
+        <f>"322457330375"</f>
+        <v>322457330375</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="str">
+        <f>"10053464760522"</f>
+        <v>10053464760522</v>
+      </c>
+      <c r="E5" t="str">
+        <f>"20251102014741140018161002610149"</f>
+        <v>20251102014741140018161002610149</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1">
+        <v>45951.2756481481</v>
+      </c>
+      <c r="H5" s="1">
+        <v>45951.2778240741</v>
+      </c>
+      <c r="I5" s="1">
+        <v>45963.5418634259</v>
+      </c>
+      <c r="J5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5">
+        <v>23.67</v>
+      </c>
+      <c r="L5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5">
+        <v>782412</v>
+      </c>
+      <c r="T5" t="s">
+        <v>40</v>
+      </c>
+      <c r="U5">
+        <v>20251101</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:22">
+      <c r="A6" t="str">
+        <f>"317981868753"</f>
+        <v>317981868753</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="str">
+        <f>"68404112834"</f>
+        <v>68404112834</v>
+      </c>
+      <c r="E6" t="str">
+        <f>"20251102014741140018161002610155"</f>
+        <v>20251102014741140018161002610155</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="1">
+        <v>45954.3706712963</v>
+      </c>
+      <c r="H6" s="1">
+        <v>45954.3729861111</v>
+      </c>
+      <c r="I6" s="1">
+        <v>45963.5418634259</v>
+      </c>
+      <c r="J6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6">
+        <v>96</v>
+      </c>
+      <c r="L6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O6">
+        <v>782412</v>
+      </c>
+      <c r="T6" t="s">
+        <v>40</v>
+      </c>
+      <c r="U6">
+        <v>20251101</v>
+      </c>
+      <c r="V6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:22">
+      <c r="A7" t="str">
+        <f>"323616093412"</f>
+        <v>323616093412</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="str">
+        <f>"0"</f>
+        <v>0</v>
+      </c>
+      <c r="E7" t="str">
+        <f>"20251102014741140018161002610171"</f>
+        <v>20251102014741140018161002610171</v>
+      </c>
+      <c r="G7" s="1">
+        <v>45962.3315740741</v>
+      </c>
+      <c r="H7" s="1">
+        <v>45962.3317476852</v>
+      </c>
+      <c r="I7" s="1">
+        <v>45963.5418634259</v>
+      </c>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7">
+        <v>-0.56</v>
+      </c>
+      <c r="L7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7">
+        <v>782412</v>
+      </c>
+      <c r="S7" t="s">
+        <v>44</v>
+      </c>
+      <c r="T7" t="s">
+        <v>29</v>
+      </c>
+      <c r="U7">
+        <v>20251101</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:22">
+      <c r="A8" t="str">
+        <f>"322001076847"</f>
+        <v>322001076847</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="str">
+        <f>"54554109984"</f>
+        <v>54554109984</v>
+      </c>
+      <c r="E8" t="str">
+        <f>"20251102014741140018161002610181"</f>
+        <v>20251102014741140018161002610181</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="1">
+        <v>45962.4370833333</v>
+      </c>
+      <c r="H8" s="1">
+        <v>45962.4377893519</v>
+      </c>
+      <c r="I8" s="1">
+        <v>45963.5418634259</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8">
+        <v>1.27</v>
+      </c>
+      <c r="L8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" t="s">
+        <v>39</v>
+      </c>
+      <c r="N8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O8">
+        <v>782412</v>
+      </c>
+      <c r="T8" t="s">
+        <v>40</v>
+      </c>
+      <c r="U8">
+        <v>20251101</v>
+      </c>
+      <c r="V8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:22">
+      <c r="A9" t="str">
+        <f>"323285870766"</f>
+        <v>323285870766</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="str">
+        <f>"10024508511818"</f>
+        <v>10024508511818</v>
+      </c>
+      <c r="E9" t="str">
+        <f>"20251102014741140018161002610181"</f>
+        <v>20251102014741140018161002610181</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="1">
+        <v>45958.5214699074</v>
+      </c>
+      <c r="H9" s="1">
+        <v>45958.5239814815</v>
+      </c>
+      <c r="I9" s="1">
+        <v>45963.5418634259</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9">
+        <v>-0.48</v>
+      </c>
+      <c r="L9" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O9">
+        <v>782412</v>
+      </c>
+      <c r="T9" t="s">
+        <v>29</v>
+      </c>
+      <c r="U9">
+        <v>20251101</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="7:9">
+    <row r="11" spans="1:22">
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="7:9">
+    <row r="12" spans="1:22">
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="7:9">
+    <row r="13" spans="1:22">
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="7:9">
+    <row r="14" spans="1:22">
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="7:9">
+    <row r="15" spans="1:22">
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="7:9">
+    <row r="16" spans="1:22">
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1377,47 +1900,361 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="10.6428571428571" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="11.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="22.7857142857143" customWidth="1"/>
     <col min="5" max="5" width="36.3571428571429" customWidth="1"/>
-    <col min="6" max="6" width="13.2142857142857" customWidth="1"/>
-    <col min="9" max="9" width="132.428571428571" customWidth="1"/>
+    <col min="6" max="8" width="13.2142857142857" customWidth="1"/>
+    <col min="9" max="9" width="51.9285714285714" customWidth="1"/>
+    <col min="10" max="10" width="12.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="G1" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H1" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="I1" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="J1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="str">
+        <f t="shared" ref="A2:A9" si="0">"140018661"</f>
+        <v>140018661</v>
+      </c>
+      <c r="B2" t="str">
+        <f t="shared" ref="B2:B8" si="1">"140018161662"</f>
+        <v>140018161662</v>
+      </c>
+      <c r="C2" t="str">
+        <f t="shared" ref="C2:C9" si="2">"XX旗舰店"</f>
+        <v>XX旗舰店</v>
+      </c>
+      <c r="D2" t="str">
+        <f>"2025-11-31 16:22:38"</f>
+        <v>2025-11-31 16:22:38</v>
+      </c>
+      <c r="E2" t="str">
+        <f>"20250731239925073116223803735"</f>
+        <v>20250731239925073116223803735</v>
+      </c>
+      <c r="F2">
+        <v>369278.63</v>
+      </c>
+      <c r="G2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2">
+        <v>12.8</v>
+      </c>
+      <c r="I2" t="str">
+        <f>"售后服务单号3191462649，对应订单号319685250747"</f>
+        <v>售后服务单号3191462649，对应订单号319685250747</v>
+      </c>
+      <c r="J2" t="str">
+        <f t="shared" ref="J2:J9" si="3">"2025-11-30"</f>
+        <v>2025-11-30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="str">
+        <f t="shared" si="0"/>
+        <v>140018661</v>
+      </c>
+      <c r="B3" t="str">
+        <f t="shared" si="1"/>
+        <v>140018161662</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" si="2"/>
+        <v>XX旗舰店</v>
+      </c>
+      <c r="D3" t="str">
+        <f>"2025-11-31 14:37:59"</f>
+        <v>2025-11-31 14:37:59</v>
+      </c>
+      <c r="E3" t="str">
+        <f>"20250731238125073114375903992"</f>
+        <v>20250731238125073114375903992</v>
+      </c>
+      <c r="F3">
+        <v>369406.33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3">
+        <v>12.8</v>
+      </c>
+      <c r="I3" t="str">
+        <f>"售后服务单号3192030743，对应订单号329826626816"</f>
+        <v>售后服务单号3192030743，对应订单号329826626816</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" si="3"/>
+        <v>2025-11-30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="str">
+        <f t="shared" si="0"/>
+        <v>140018661</v>
+      </c>
+      <c r="B4" t="str">
+        <f t="shared" si="1"/>
+        <v>140018161662</v>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" si="2"/>
+        <v>XX旗舰店</v>
+      </c>
+      <c r="D4" t="str">
+        <f>"2025-11-31 12:56:43"</f>
+        <v>2025-11-31 12:56:43</v>
+      </c>
+      <c r="E4" t="str">
+        <f>"20250731014656140018161002148898"</f>
+        <v>20250731014656140018161002148898</v>
+      </c>
+      <c r="F4">
+        <v>369419.13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4">
+        <v>1177.03</v>
+      </c>
+      <c r="I4" t="str">
+        <f>"2025年7月30日费项"</f>
+        <v>2025年7月30日费项</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="3"/>
+        <v>2025-11-30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="str">
+        <f t="shared" si="0"/>
+        <v>140018661</v>
+      </c>
+      <c r="B5" t="str">
+        <f t="shared" si="1"/>
+        <v>140018161662</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="2"/>
+        <v>XX旗舰店</v>
+      </c>
+      <c r="D5" t="str">
+        <f>"2025-11-31 12:56:43"</f>
+        <v>2025-11-31 12:56:43</v>
+      </c>
+      <c r="E5" t="str">
+        <f>"20250731014656140018161002148891"</f>
+        <v>20250731014656140018161002148891</v>
+      </c>
+      <c r="F5">
+        <v>370596.16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5">
+        <v>464.96</v>
+      </c>
+      <c r="I5" t="str">
+        <f>"2025年7月30日代收付服务费"</f>
+        <v>2025年7月30日代收付服务费</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="3"/>
+        <v>2025-11-30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="str">
+        <f t="shared" si="0"/>
+        <v>140018661</v>
+      </c>
+      <c r="B6" t="str">
+        <f t="shared" si="1"/>
+        <v>140018161662</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="2"/>
+        <v>XX旗舰店</v>
+      </c>
+      <c r="D6" t="str">
+        <f>"2025-11-31 12:56:43"</f>
+        <v>2025-11-31 12:56:43</v>
+      </c>
+      <c r="E6" t="str">
+        <f>"20250731014656140018161002148881"</f>
+        <v>20250731014656140018161002148881</v>
+      </c>
+      <c r="F6">
+        <v>371061.12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6">
+        <v>129.4</v>
+      </c>
+      <c r="I6" t="str">
+        <f>"2025年7月30日退货金额"</f>
+        <v>2025年7月30日退货金额</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="3"/>
+        <v>2025-11-30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="str">
+        <f t="shared" si="0"/>
+        <v>140018661</v>
+      </c>
+      <c r="B7" t="str">
+        <f t="shared" si="1"/>
+        <v>140018161662</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="2"/>
+        <v>XX旗舰店</v>
+      </c>
+      <c r="D7" t="str">
+        <f>"2025-11-31 12:56:43"</f>
+        <v>2025-11-31 12:56:43</v>
+      </c>
+      <c r="E7" t="str">
+        <f>"20250731014656140018161002148905"</f>
+        <v>20250731014656140018161002148905</v>
+      </c>
+      <c r="F7">
+        <v>371190.52</v>
+      </c>
+      <c r="G7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7">
+        <v>44.74</v>
+      </c>
+      <c r="I7" t="str">
+        <f>"2025年7月30日费项"</f>
+        <v>2025年7月30日费项</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="3"/>
+        <v>2025-11-30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="str">
+        <f t="shared" si="0"/>
+        <v>140018661</v>
+      </c>
+      <c r="B8" t="str">
+        <f t="shared" si="1"/>
+        <v>140018161662</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="2"/>
+        <v>XX旗舰店</v>
+      </c>
+      <c r="D8" t="str">
+        <f>"2025-11-31 12:56:43"</f>
+        <v>2025-11-31 12:56:43</v>
+      </c>
+      <c r="E8" t="str">
+        <f>"20250731014656140018161002148874"</f>
+        <v>20250731014656140018161002148874</v>
+      </c>
+      <c r="F8">
+        <v>371235.26</v>
+      </c>
+      <c r="G8">
+        <v>6727.37</v>
+      </c>
+      <c r="H8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" t="str">
+        <f>"2025年7月30日微信等其他支付方式货款"</f>
+        <v>2025年7月30日微信等其他支付方式货款</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="3"/>
+        <v>2025-11-30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="str">
+        <f t="shared" si="0"/>
+        <v>140018661</v>
+      </c>
+      <c r="B9" t="str">
+        <f>"140018161662"</f>
+        <v>140018161662</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="2"/>
+        <v>XX旗舰店</v>
+      </c>
+      <c r="D9" t="str">
+        <f>"2025-11-31 12:56:43"</f>
+        <v>2025-11-31 12:56:43</v>
+      </c>
+      <c r="E9" t="str">
+        <f>"20250731014656140018161002148868"</f>
+        <v>20250731014656140018161002148868</v>
+      </c>
+      <c r="F9">
+        <v>364507.89</v>
+      </c>
+      <c r="G9">
+        <v>16286.04</v>
+      </c>
+      <c r="H9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" t="str">
+        <f>"2025年7月30日京东支付货款"</f>
+        <v>2025年7月30日京东支付货款</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="3"/>
+        <v>2025-11-30</v>
       </c>
     </row>
   </sheetData>
